--- a/Спорт Москвы — домашние матчи, сентябрь-октябрь 2026.xlsx
+++ b/Спорт Москвы — домашние матчи, сентябрь-октябрь 2026.xlsx
@@ -1145,7 +1145,11 @@
       <c r="G14" s="13" t="inlineStr"/>
       <c r="H14" s="13" t="inlineStr"/>
       <c r="I14" s="13" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>Спартак 19:30</t>
+        </is>
+      </c>
       <c r="K14" s="13" t="inlineStr"/>
       <c r="L14" s="13" t="inlineStr"/>
       <c r="M14" s="13" t="inlineStr"/>
@@ -1182,10 +1186,14 @@
       <c r="O15" s="13" t="inlineStr"/>
       <c r="P15" s="13" t="inlineStr">
         <is>
-          <t>Красная Армия 18:30</t>
-        </is>
-      </c>
-      <c r="Q15" s="13" t="inlineStr"/>
+          <t>Красная Армия</t>
+        </is>
+      </c>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>Академия Михайлова</t>
+        </is>
+      </c>
       <c r="R15" s="13" t="inlineStr"/>
       <c r="S15" s="13" t="inlineStr"/>
       <c r="T15" s="13" t="inlineStr"/>
@@ -1207,8 +1215,16 @@
       <c r="G16" s="13" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
       <c r="I16" s="13" t="inlineStr"/>
-      <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>Торпедо 19:30</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Адмирал 19:30</t>
+        </is>
+      </c>
       <c r="L16" s="13" t="inlineStr"/>
       <c r="M16" s="13" t="inlineStr"/>
       <c r="N16" s="13" t="inlineStr"/>
@@ -1280,7 +1296,11 @@
       <c r="N18" s="13" t="inlineStr"/>
       <c r="O18" s="13" t="inlineStr"/>
       <c r="P18" s="13" t="inlineStr"/>
-      <c r="Q18" s="13" t="inlineStr"/>
+      <c r="Q18" s="13" t="inlineStr">
+        <is>
+          <t>МХК Спартак</t>
+        </is>
+      </c>
       <c r="R18" s="13" t="inlineStr"/>
       <c r="S18" s="13" t="inlineStr"/>
       <c r="T18" s="13" t="inlineStr"/>
@@ -1302,7 +1322,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Оренбург 18:30 (РЖД Арена)</t>
+          <t>Оренбург 18:30</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr"/>
@@ -1341,7 +1361,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Ростов 14:00</t>
+          <t>Ростов 17:00</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr"/>
@@ -1362,7 +1382,11 @@
       <c r="N20" s="15" t="inlineStr"/>
       <c r="O20" s="15" t="inlineStr"/>
       <c r="P20" s="15" t="inlineStr"/>
-      <c r="Q20" s="15" t="inlineStr"/>
+      <c r="Q20" s="15" t="inlineStr">
+        <is>
+          <t>Красная Армия</t>
+        </is>
+      </c>
       <c r="R20" s="15" t="inlineStr"/>
       <c r="S20" s="15" t="inlineStr"/>
       <c r="T20" s="15" t="inlineStr"/>
@@ -1389,11 +1413,7 @@
       <c r="L21" s="13" t="inlineStr"/>
       <c r="M21" s="13" t="inlineStr"/>
       <c r="N21" s="13" t="inlineStr"/>
-      <c r="O21" s="13" t="inlineStr">
-        <is>
-          <t>МХК Динамо М 18:30</t>
-        </is>
-      </c>
+      <c r="O21" s="13" t="inlineStr"/>
       <c r="P21" s="13" t="inlineStr"/>
       <c r="Q21" s="13" t="inlineStr"/>
       <c r="R21" s="13" t="inlineStr"/>
@@ -1425,7 +1445,11 @@
       <c r="O22" s="13" t="inlineStr"/>
       <c r="P22" s="13" t="inlineStr"/>
       <c r="Q22" s="13" t="inlineStr"/>
-      <c r="R22" s="13" t="inlineStr"/>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>Красная Машина Атлант</t>
+        </is>
+      </c>
       <c r="S22" s="13" t="inlineStr"/>
       <c r="T22" s="13" t="inlineStr"/>
       <c r="U22" s="13" t="inlineStr"/>
@@ -1465,7 +1489,7 @@
       <c r="N23" s="13" t="inlineStr"/>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>Академия Михайлова 18:30</t>
+          <t>Академия Михайлова</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr"/>
@@ -1567,7 +1591,11 @@
       <c r="M26" s="15" t="inlineStr"/>
       <c r="N26" s="15" t="inlineStr"/>
       <c r="O26" s="15" t="inlineStr"/>
-      <c r="P26" s="15" t="inlineStr"/>
+      <c r="P26" s="15" t="inlineStr">
+        <is>
+          <t>Академия СКА</t>
+        </is>
+      </c>
       <c r="Q26" s="15" t="inlineStr"/>
       <c r="R26" s="15" t="inlineStr"/>
       <c r="S26" s="15" t="inlineStr"/>
@@ -1632,8 +1660,16 @@
       <c r="L28" s="13" t="inlineStr"/>
       <c r="M28" s="13" t="inlineStr"/>
       <c r="N28" s="13" t="inlineStr"/>
-      <c r="O28" s="13" t="inlineStr"/>
-      <c r="P28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>Академия СКА</t>
+        </is>
+      </c>
+      <c r="P28" s="13" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
       <c r="Q28" s="13" t="inlineStr"/>
       <c r="R28" s="13" t="inlineStr"/>
       <c r="S28" s="13" t="inlineStr"/>
@@ -1702,7 +1738,11 @@
       <c r="L30" s="13" t="inlineStr"/>
       <c r="M30" s="13" t="inlineStr"/>
       <c r="N30" s="13" t="inlineStr"/>
-      <c r="O30" s="13" t="inlineStr"/>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>Авто</t>
+        </is>
+      </c>
       <c r="P30" s="13" t="inlineStr"/>
       <c r="Q30" s="13" t="inlineStr"/>
       <c r="R30" s="13" t="inlineStr"/>
@@ -1777,7 +1817,11 @@
       <c r="M32" s="13" t="inlineStr"/>
       <c r="N32" s="13" t="inlineStr"/>
       <c r="O32" s="13" t="inlineStr"/>
-      <c r="P32" s="13" t="inlineStr"/>
+      <c r="P32" s="13" t="inlineStr">
+        <is>
+          <t>Динамо-Шинник</t>
+        </is>
+      </c>
       <c r="Q32" s="13" t="inlineStr"/>
       <c r="R32" s="13" t="inlineStr"/>
       <c r="S32" s="13" t="inlineStr"/>
@@ -1851,8 +1895,16 @@
       <c r="M34" s="15" t="inlineStr"/>
       <c r="N34" s="15" t="inlineStr"/>
       <c r="O34" s="15" t="inlineStr"/>
-      <c r="P34" s="15" t="inlineStr"/>
-      <c r="Q34" s="15" t="inlineStr"/>
+      <c r="P34" s="15" t="inlineStr">
+        <is>
+          <t>Динамо-Шинник</t>
+        </is>
+      </c>
+      <c r="Q34" s="15" t="inlineStr">
+        <is>
+          <t>Красная Машина Атлант</t>
+        </is>
+      </c>
       <c r="R34" s="15" t="inlineStr"/>
       <c r="S34" s="15" t="inlineStr"/>
       <c r="T34" s="15" t="inlineStr">
@@ -1920,7 +1972,11 @@
       <c r="L36" s="13" t="inlineStr"/>
       <c r="M36" s="13" t="inlineStr"/>
       <c r="N36" s="13" t="inlineStr"/>
-      <c r="O36" s="13" t="inlineStr"/>
+      <c r="O36" s="13" t="inlineStr">
+        <is>
+          <t>Динамо-Шинник</t>
+        </is>
+      </c>
       <c r="P36" s="13" t="inlineStr"/>
       <c r="Q36" s="13" t="inlineStr"/>
       <c r="R36" s="13" t="inlineStr"/>
@@ -1963,7 +2019,11 @@
       </c>
       <c r="O37" s="13" t="inlineStr"/>
       <c r="P37" s="13" t="inlineStr"/>
-      <c r="Q37" s="13" t="inlineStr"/>
+      <c r="Q37" s="13" t="inlineStr">
+        <is>
+          <t>Красная Машина Юниор</t>
+        </is>
+      </c>
       <c r="R37" s="13" t="inlineStr"/>
       <c r="S37" s="13" t="inlineStr"/>
       <c r="T37" s="13" t="inlineStr"/>
@@ -2002,10 +2062,10 @@
         <v>1</v>
       </c>
       <c r="J38" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L38" s="17" t="n">
         <v>5</v>
@@ -2017,16 +2077,16 @@
         <v>5</v>
       </c>
       <c r="O38" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P38" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R38" s="17" t="n">
         <v>1</v>
-      </c>
-      <c r="Q38" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="17" t="n">
-        <v>0</v>
       </c>
       <c r="S38" s="17" t="n">
         <v>2</v>
@@ -2047,7 +2107,7 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>Итого домашних матчей за месяц: 40</t>
+          <t>Итого домашних матчей за месяц: 55</t>
         </is>
       </c>
     </row>
@@ -2460,10 +2520,18 @@
       <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="13" t="inlineStr"/>
       <c r="N8" s="13" t="inlineStr"/>
-      <c r="O8" s="13" t="inlineStr"/>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>Динамо-Шинник</t>
+        </is>
+      </c>
       <c r="P8" s="13" t="inlineStr"/>
       <c r="Q8" s="13" t="inlineStr"/>
-      <c r="R8" s="13" t="inlineStr"/>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>Алмаз</t>
+        </is>
+      </c>
       <c r="S8" s="13" t="inlineStr"/>
       <c r="T8" s="13" t="inlineStr"/>
       <c r="U8" s="13" t="inlineStr">
@@ -2508,7 +2576,11 @@
       <c r="O9" s="13" t="inlineStr"/>
       <c r="P9" s="13" t="inlineStr"/>
       <c r="Q9" s="13" t="inlineStr"/>
-      <c r="R9" s="13" t="inlineStr"/>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>Алмаз</t>
+        </is>
+      </c>
       <c r="S9" s="13" t="inlineStr"/>
       <c r="T9" s="13" t="inlineStr"/>
       <c r="U9" s="13" t="inlineStr"/>
@@ -2614,8 +2686,16 @@
       <c r="N12" s="13" t="inlineStr"/>
       <c r="O12" s="13" t="inlineStr"/>
       <c r="P12" s="13" t="inlineStr"/>
-      <c r="Q12" s="13" t="inlineStr"/>
-      <c r="R12" s="13" t="inlineStr"/>
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t>СКА-1946</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="inlineStr">
+        <is>
+          <t>Академия Михайлова</t>
+        </is>
+      </c>
       <c r="S12" s="13" t="inlineStr"/>
       <c r="T12" s="13" t="inlineStr"/>
       <c r="U12" s="13" t="inlineStr"/>
@@ -2643,7 +2723,11 @@
       <c r="N13" s="13" t="inlineStr"/>
       <c r="O13" s="13" t="inlineStr"/>
       <c r="P13" s="13" t="inlineStr"/>
-      <c r="Q13" s="13" t="inlineStr"/>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>СКА-1946</t>
+        </is>
+      </c>
       <c r="R13" s="13" t="inlineStr"/>
       <c r="S13" s="13" t="inlineStr"/>
       <c r="T13" s="13" t="inlineStr"/>
@@ -2757,7 +2841,11 @@
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr"/>
-      <c r="C17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Родина (время уточняется)</t>
+        </is>
+      </c>
       <c r="D17" s="15" t="inlineStr"/>
       <c r="E17" s="15" t="inlineStr"/>
       <c r="F17" s="15" t="inlineStr"/>
@@ -2771,7 +2859,11 @@
       <c r="N17" s="15" t="inlineStr"/>
       <c r="O17" s="15" t="inlineStr"/>
       <c r="P17" s="15" t="inlineStr"/>
-      <c r="Q17" s="15" t="inlineStr"/>
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>МХК Динамо СПб</t>
+        </is>
+      </c>
       <c r="R17" s="15" t="inlineStr"/>
       <c r="S17" s="15" t="inlineStr"/>
       <c r="T17" s="15" t="inlineStr">
@@ -2790,11 +2882,7 @@
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr"/>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Родина 16:30</t>
-        </is>
-      </c>
+      <c r="C18" s="15" t="inlineStr"/>
       <c r="D18" s="15" t="inlineStr"/>
       <c r="E18" s="15" t="inlineStr"/>
       <c r="F18" s="15" t="inlineStr"/>
@@ -2813,7 +2901,11 @@
       <c r="O18" s="15" t="inlineStr"/>
       <c r="P18" s="15" t="inlineStr"/>
       <c r="Q18" s="15" t="inlineStr"/>
-      <c r="R18" s="15" t="inlineStr"/>
+      <c r="R18" s="15" t="inlineStr">
+        <is>
+          <t>Мамонты Югры</t>
+        </is>
+      </c>
       <c r="S18" s="15" t="inlineStr">
         <is>
           <t>Локомотив-Кубань</t>
@@ -2845,7 +2937,11 @@
       <c r="N19" s="13" t="inlineStr"/>
       <c r="O19" s="13" t="inlineStr"/>
       <c r="P19" s="13" t="inlineStr"/>
-      <c r="Q19" s="13" t="inlineStr"/>
+      <c r="Q19" s="13" t="inlineStr">
+        <is>
+          <t>МХК Динамо СПб</t>
+        </is>
+      </c>
       <c r="R19" s="13" t="inlineStr"/>
       <c r="S19" s="13" t="inlineStr"/>
       <c r="T19" s="13" t="inlineStr"/>
@@ -2868,14 +2964,22 @@
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr"/>
-      <c r="C20" s="13" t="inlineStr"/>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Ростов (КР, время уточняется)</t>
+        </is>
+      </c>
       <c r="D20" s="13" t="inlineStr"/>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Акрон (КР) 18:30</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr"/>
+          <t>Акрон (КР, время уточняется)</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Спартак (КР, время уточняется)</t>
+        </is>
+      </c>
       <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
       <c r="I20" s="13" t="inlineStr"/>
@@ -2905,11 +3009,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Ростов (КР) 20:45</t>
-        </is>
-      </c>
+      <c r="C21" s="13" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr"/>
       <c r="E21" s="13" t="inlineStr"/>
       <c r="F21" s="13" t="inlineStr"/>
@@ -2926,7 +3026,11 @@
       <c r="M21" s="13" t="inlineStr"/>
       <c r="N21" s="13" t="inlineStr"/>
       <c r="O21" s="13" t="inlineStr"/>
-      <c r="P21" s="13" t="inlineStr"/>
+      <c r="P21" s="13" t="inlineStr">
+        <is>
+          <t>Красная Машина Атлант</t>
+        </is>
+      </c>
       <c r="Q21" s="13" t="inlineStr"/>
       <c r="R21" s="13" t="inlineStr"/>
       <c r="S21" s="13" t="inlineStr"/>
@@ -2945,11 +3049,7 @@
       <c r="C22" s="13" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>Спартак (КР) 20:45</t>
-        </is>
-      </c>
+      <c r="F22" s="13" t="inlineStr"/>
       <c r="G22" s="13" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="13" t="inlineStr"/>
@@ -2961,7 +3061,11 @@
       <c r="O22" s="13" t="inlineStr"/>
       <c r="P22" s="13" t="inlineStr"/>
       <c r="Q22" s="13" t="inlineStr"/>
-      <c r="R22" s="13" t="inlineStr"/>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>Кузнецкие Медведи</t>
+        </is>
+      </c>
       <c r="S22" s="13" t="inlineStr"/>
       <c r="T22" s="13" t="inlineStr"/>
       <c r="U22" s="13" t="inlineStr"/>
@@ -2987,7 +3091,11 @@
       <c r="L23" s="13" t="inlineStr"/>
       <c r="M23" s="13" t="inlineStr"/>
       <c r="N23" s="13" t="inlineStr"/>
-      <c r="O23" s="13" t="inlineStr"/>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>Красная Машина Атлант</t>
+        </is>
+      </c>
       <c r="P23" s="13" t="inlineStr"/>
       <c r="Q23" s="13" t="inlineStr"/>
       <c r="R23" s="13" t="inlineStr"/>
@@ -3003,15 +3111,27 @@
           <t>17 — Суббота</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr"/>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Рубин (время уточняется)</t>
+        </is>
+      </c>
       <c r="C24" s="15" t="inlineStr"/>
-      <c r="D24" s="15" t="inlineStr"/>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>ЦСКА (время уточняется)</t>
+        </is>
+      </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Краснодар 19:30</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr"/>
+          <t>Краснодар (время уточняется)</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Оренбург (время уточняется)</t>
+        </is>
+      </c>
       <c r="G24" s="15" t="inlineStr"/>
       <c r="H24" s="15" t="inlineStr"/>
       <c r="I24" s="15" t="inlineStr"/>
@@ -3036,17 +3156,9 @@
           <t>18 — Воскресенье</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Рубин 18:30</t>
-        </is>
-      </c>
+      <c r="B25" s="15" t="inlineStr"/>
       <c r="C25" s="15" t="inlineStr"/>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>ЦСКА 16:15</t>
-        </is>
-      </c>
+      <c r="D25" s="15" t="inlineStr"/>
       <c r="E25" s="15" t="inlineStr"/>
       <c r="F25" s="15" t="inlineStr"/>
       <c r="G25" s="15" t="inlineStr"/>
@@ -3066,8 +3178,16 @@
         </is>
       </c>
       <c r="O25" s="15" t="inlineStr"/>
-      <c r="P25" s="15" t="inlineStr"/>
-      <c r="Q25" s="15" t="inlineStr"/>
+      <c r="P25" s="15" t="inlineStr">
+        <is>
+          <t>Красная Машина Юниор</t>
+        </is>
+      </c>
+      <c r="Q25" s="15" t="inlineStr">
+        <is>
+          <t>Динамо-Шинник</t>
+        </is>
+      </c>
       <c r="R25" s="15" t="inlineStr"/>
       <c r="S25" s="15" t="inlineStr"/>
       <c r="T25" s="15" t="inlineStr"/>
@@ -3085,11 +3205,7 @@
       <c r="C26" s="13" t="inlineStr"/>
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr"/>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>Оренбург 19:30</t>
-        </is>
-      </c>
+      <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
       <c r="I26" s="13" t="inlineStr"/>
@@ -3100,7 +3216,11 @@
       <c r="N26" s="13" t="inlineStr"/>
       <c r="O26" s="13" t="inlineStr"/>
       <c r="P26" s="13" t="inlineStr"/>
-      <c r="Q26" s="13" t="inlineStr"/>
+      <c r="Q26" s="13" t="inlineStr">
+        <is>
+          <t>Динамо-Шинник</t>
+        </is>
+      </c>
       <c r="R26" s="13" t="inlineStr"/>
       <c r="S26" s="13" t="inlineStr"/>
       <c r="T26" s="13" t="inlineStr"/>
@@ -3172,7 +3292,11 @@
       </c>
       <c r="M28" s="13" t="inlineStr"/>
       <c r="N28" s="13" t="inlineStr"/>
-      <c r="O28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>Красная Машина Юниор</t>
+        </is>
+      </c>
       <c r="P28" s="13" t="inlineStr"/>
       <c r="Q28" s="13" t="inlineStr"/>
       <c r="R28" s="13" t="inlineStr"/>
@@ -3210,7 +3334,11 @@
         </is>
       </c>
       <c r="O29" s="13" t="inlineStr"/>
-      <c r="P29" s="13" t="inlineStr"/>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>Академия Михайлова</t>
+        </is>
+      </c>
       <c r="Q29" s="13" t="inlineStr"/>
       <c r="R29" s="13" t="inlineStr"/>
       <c r="S29" s="13" t="inlineStr"/>
@@ -3267,7 +3395,11 @@
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr"/>
-      <c r="C31" s="15" t="inlineStr"/>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Спартак (время уточняется)</t>
+        </is>
+      </c>
       <c r="D31" s="15" t="inlineStr"/>
       <c r="E31" s="15" t="inlineStr"/>
       <c r="F31" s="15" t="inlineStr"/>
@@ -3308,11 +3440,7 @@
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr"/>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Спартак 16:00</t>
-        </is>
-      </c>
+      <c r="C32" s="15" t="inlineStr"/>
       <c r="D32" s="15" t="inlineStr"/>
       <c r="E32" s="15" t="inlineStr"/>
       <c r="F32" s="15" t="inlineStr"/>
@@ -3328,7 +3456,11 @@
       </c>
       <c r="M32" s="15" t="inlineStr"/>
       <c r="N32" s="15" t="inlineStr"/>
-      <c r="O32" s="15" t="inlineStr"/>
+      <c r="O32" s="15" t="inlineStr">
+        <is>
+          <t>МХК Динамо М</t>
+        </is>
+      </c>
       <c r="P32" s="15" t="inlineStr"/>
       <c r="Q32" s="15" t="inlineStr"/>
       <c r="R32" s="15" t="inlineStr"/>
@@ -3381,8 +3513,16 @@
           <t>27 — Вторник</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr"/>
-      <c r="C34" s="13" t="inlineStr"/>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Рубин (КР, время уточняется)</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Локомотив (КР, время уточняется)</t>
+        </is>
+      </c>
       <c r="D34" s="13" t="inlineStr"/>
       <c r="E34" s="13" t="inlineStr"/>
       <c r="F34" s="13" t="inlineStr"/>
@@ -3395,7 +3535,11 @@
       <c r="M34" s="13" t="inlineStr"/>
       <c r="N34" s="13" t="inlineStr"/>
       <c r="O34" s="13" t="inlineStr"/>
-      <c r="P34" s="13" t="inlineStr"/>
+      <c r="P34" s="13" t="inlineStr">
+        <is>
+          <t>Красная Армия</t>
+        </is>
+      </c>
       <c r="Q34" s="13" t="inlineStr"/>
       <c r="R34" s="13" t="inlineStr"/>
       <c r="S34" s="13" t="inlineStr">
@@ -3414,11 +3558,7 @@
           <t>28 — Среда</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>Рубин (КР) 20:30</t>
-        </is>
-      </c>
+      <c r="B35" s="13" t="inlineStr"/>
       <c r="C35" s="13" t="inlineStr"/>
       <c r="D35" s="13" t="inlineStr"/>
       <c r="E35" s="13" t="inlineStr"/>
@@ -3456,11 +3596,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr"/>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Локомотив (КР) 19:30</t>
-        </is>
-      </c>
+      <c r="C36" s="13" t="inlineStr"/>
       <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="13" t="inlineStr"/>
       <c r="F36" s="13" t="inlineStr"/>
@@ -3521,13 +3657,17 @@
       <c r="C38" s="15" t="inlineStr"/>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Ахмат 17:30</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr"/>
+          <t>Ахмат (время уточняется)</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Спартак (время уточняется)</t>
+        </is>
+      </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Краснодар 19:45</t>
+          <t>Краснодар (время уточняется)</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr"/>
@@ -3541,7 +3681,11 @@
       <c r="O38" s="15" t="inlineStr"/>
       <c r="P38" s="15" t="inlineStr"/>
       <c r="Q38" s="15" t="inlineStr"/>
-      <c r="R38" s="15" t="inlineStr"/>
+      <c r="R38" s="15" t="inlineStr">
+        <is>
+          <t>МХК Спартак</t>
+        </is>
+      </c>
       <c r="S38" s="15" t="inlineStr"/>
       <c r="T38" s="15" t="inlineStr"/>
       <c r="U38" s="15" t="inlineStr"/>
@@ -3568,7 +3712,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="17" t="n">
         <v>3</v>
@@ -3598,16 +3742,16 @@
         <v>4</v>
       </c>
       <c r="O39" s="17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" s="17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R39" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S39" s="17" t="n">
         <v>4</v>
@@ -3628,7 +3772,7 @@
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>Итого домашних матчей за месяц: 54</t>
+          <t>Итого домашних матчей за месяц: 75</t>
         </is>
       </c>
     </row>
@@ -3900,14 +4044,14 @@
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Источники данных — только официальные сайты лиг и клубов</t>
+          <t>Источники данных</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Данные собраны 29.08.2026.</t>
+          <t>Основной источник — официальные сайты и API лиг и клубов. Football/КХЛ/МХЛ дополнительно сверены и датированы по championat.com (данные собраны 29–30.08.2026); там, где championat расходился с сайтом клуба, приоритет отдан championat как более полному и структурированному источнику (см. лист «Замечания», пункт 8).</t>
         </is>
       </c>
     </row>
@@ -3961,7 +4105,7 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>https://rodina.moscow/tickets · https://fc-rostov.ru/matches · https://fakelfc.ru/matches · https://rubin-kazan.ru/calendar/upcoming/</t>
+          <t>https://www.championat.com/football/_russiapl/tournament/7096/calendar/ · https://www.championat.com/football/_russiacup/tournament/7094/calendar/</t>
         </is>
       </c>
     </row>
@@ -3988,7 +4132,7 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>https://pfc-cska.com/ru/matchi/kalendar-matchej/</t>
+          <t>https://www.championat.com/football/_russiapl/tournament/7096/calendar/ · https://pfc-cska.com/ru/matchi/kalendar-matchej/</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4159,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>https://fcdynamo.ru/fixtures/dynamo/calendar/ (ICS: https://fcdynamo.ru/calendar/dynamo)</t>
+          <t>https://www.championat.com/football/_russiapl/tournament/7096/calendar/ · https://fcdynamo.ru/calendar/dynamo (ICS)</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4186,7 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>https://www.fclm.ru/schedule/</t>
+          <t>https://www.championat.com/football/_russiapl/tournament/7096/calendar/ · https://www.fclm.ru/schedule/</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4213,7 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>https://rodina.moscow/tickets</t>
+          <t>https://www.championat.com/football/_russiapl/tournament/7096/calendar/ · https://rodina.moscow/tickets</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4321,7 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>https://www.khl.ru/calendar/ (API khl.api.webcaster.pro)</t>
+          <t>API khl.api.webcaster.pro (khl.ru) · https://www.championat.com/hockey/_superleague/tournament/7092/calendar/</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4348,7 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>https://www.khl.ru/calendar/ (API khl.api.webcaster.pro)</t>
+          <t>API khl.api.webcaster.pro (khl.ru) · https://www.championat.com/hockey/_superleague/tournament/7092/calendar/</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4375,7 @@
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>https://www.khl.ru/calendar/ (API khl.api.webcaster.pro)</t>
+          <t>API khl.api.webcaster.pro (khl.ru) · https://www.championat.com/hockey/_superleague/tournament/7092/calendar/</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4456,7 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>https://redarmy.cska-hockey.ru/calendar/</t>
+          <t>https://www.championat.com/hockey/_mhl/tournament/7270/calendar/</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4483,7 @@
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>https://mhl.spartak.ru/matches/calendar/</t>
+          <t>https://www.championat.com/hockey/_mhl/tournament/7270/calendar/</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4510,7 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>календарь не опубликован</t>
+          <t>https://www.championat.com/hockey/_mhl/tournament/7270/calendar/</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4537,7 @@
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>календарь не опубликован</t>
+          <t>https://www.championat.com/hockey/_mhl/tournament/7270/calendar/</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -4590,64 +4734,71 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>2. Баскетбол. Единая лига ВТБ, Суперлига и женская Премьер-лига опубликовали даты, но не время начала матчей. Время появится ближе к турам.</t>
+          <t>2. Время матчей РПЛ и Кубка России с 10.10.2026 и позже показано как «время уточняется»: championat.com на эти туры даёт одинаковое время для всех матчей тура — это заглушка, реальные слоты вещания объявляют позже. Дата при этом точная (тур назначен).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>3. МХЛ. На 29.08.2026 опубликована только стартовая часть календаря сезона 2026/27: подтверждены три матча (8, 14 и 16 сентября). Календарь МХК «Динамо М» и «Крыльев Советов» не опубликован — колонки оставлены пустыми.</t>
+          <t>3. Баскетбол. Единая лига ВТБ, Суперлига и женская Премьер-лига опубликовали даты, но не время начала матчей. Время появится ближе к турам.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>4. Кубок России по футболу (КР) и Суперкубок Единой лиги ВТБ (СК) включены: это тоже домашние матчи этих клубов в Москве.</t>
+          <t>4. МХЛ. Полный календарь взят с championat.com — прямые сайты клубов (redarmy.cska-hockey.ru, mhl.spartak.ru) публикуют только ближайшие 2–3 игры и для полной картины сентября–октября не годились. Время начала (18:00/19:00) в МХЛ обычно стандартное для тура, но может измениться.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>5. Суперкубок Единой лиги ВТБ 17–20.09 целиком проходит в Москве на «ВТБ Арене». В таблице отмечены только матчи ЦСКА; в те же дни там играют УНИКС, «Зенит», «Локомотив-Кубань», «Анадолу Эфес», «Игокеа» — всего 9 матчей.</t>
+          <t>5. Кубок России по футболу (КР) и Суперкубок Единой лиги ВТБ (СК) включены: это тоже домашние матчи этих клубов в Москве.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>6. Не все клубы играют в самой Москве: «Родина» и «Торпедо» — «Арена Химки», «Велес» — Домодедово, «Химик» — Воскресенск. Арена указана в шапке каждой колонки.</t>
+          <t>6. Суперкубок Единой лиги ВТБ 17–20.09 целиком проходит в Москве на «ВТБ Арене». В таблице отмечены только матчи ЦСКА; в те же дни там играют УНИКС, «Зенит», «Локомотив-Кубань», «Анадолу Эфес», «Игокеа» — всего 9 матчей.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>7. «Динамо» (футбол) 12.09 принимает «Оренбург» на «РЖД Арене» — по данным официального календаря клуба. На сайте «Оренбурга» для этого матча указана «ВТБ Арена»; данные клуба-хозяина приняты как приоритетные.</t>
+          <t>7. Не все клубы играют в самой Москве: «Родина» и «Торпедо» — «Арена Химки», «Велес» — Домодедово, «Химик» — Воскресенск. Арена указана в шапке каждой колонки.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>8. Официальные сайты РПЛ (premierliga.ru) и ФК «Спартак» (spartak.com) закрыты капчей. Домашние матчи «Спартака» восстановлены по официальным календарям соперников: «Родина», «Ростов», «Факел», «Рубин».</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="25" t="inlineStr"/>
+          <t>8. «Динамо» (футбол) 12.09 принимает «Оренбург» — по данным championat и официального календаря клуба это «РЖД Арена». На сайте «Оренбурга» указана «ВТБ Арена» — вероятно, устаревшая информация; данные клуба-хозяина и championat приняты как приоритетные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>9. Проверка через championat.com (29–30.08.2026) выявила и исправила ошибки в датах, взятых с сайтов клубов (расхождения на 1 день у ЦСКА, «Родины», «Спартака» — вероятно, из-за смещения при парсинге виджетов календаря на клубных сайтах) и добавила три пропущенных матча КХЛ (7 и 9 сентября). Официальные сайты РПЛ (premierliga.ru) и ФК «Спартак» (spartak.com) закрыты капчей — их данные заменены на championat.com и календари соперников.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Обозначения</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>(КР) — Кубок России, (СК) — Суперкубок. Время указано московское. Выходные дни подсвечены.</t>
         </is>

--- a/Спорт Москвы — домашние матчи, сентябрь-октябрь 2026.xlsx
+++ b/Спорт Москвы — домашние матчи, сентябрь-октябрь 2026.xlsx
@@ -1085,7 +1085,11 @@
       <c r="I12" s="15" t="inlineStr"/>
       <c r="J12" s="15" t="inlineStr"/>
       <c r="K12" s="15" t="inlineStr"/>
-      <c r="L12" s="15" t="inlineStr"/>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>Торпедо 17:00</t>
+        </is>
+      </c>
       <c r="M12" s="15" t="inlineStr"/>
       <c r="N12" s="15" t="inlineStr"/>
       <c r="O12" s="15" t="inlineStr"/>
@@ -2068,7 +2072,7 @@
         <v>6</v>
       </c>
       <c r="L38" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M38" s="17" t="n">
         <v>6</v>
@@ -2107,7 +2111,7 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>Итого домашних матчей за месяц: 55</t>
+          <t>Итого домашних матчей за месяц: 56</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4787,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>9. Проверка через championat.com (29–30.08.2026) выявила и исправила ошибки в датах, взятых с сайтов клубов (расхождения на 1 день у ЦСКА, «Родины», «Спартака» — вероятно, из-за смещения при парсинге виджетов календаря на клубных сайтах) и добавила три пропущенных матча КХЛ (7 и 9 сентября). Официальные сайты РПЛ (premierliga.ru) и ФК «Спартак» (spartak.com) закрыты капчей — их данные заменены на championat.com и календари соперников.</t>
+          <t>9. Проверка через championat.com (29–30.08.2026) выявила и исправила ошибки в датах, взятых с сайтов клубов (расхождения на 1 день у ЦСКА, «Родины», «Спартака» — вероятно, из-за смещения при парсинге виджетов календаря на клубных сайтах) и добавила четыре пропущенных матча КХЛ, включая открытие сезона 05.09 (Спартак — Торпедо): при первом сборе через официальный API не хватило страниц пагинации, часть календаря не попала в выборку. Официальные сайты РПЛ (premierliga.ru) и ФК «Спартак» (spartak.com) закрыты капчей — их данные заменены на championat.com и календари соперников.</t>
         </is>
       </c>
     </row>
